--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128462844</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128462848</v>
       </c>
       <c r="B3" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128462835</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128462828</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128462822</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128462856</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1402,6 +1402,257 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128582282</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547270</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6323302</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128582313</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547209</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6323428</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>stöttes</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1654,6 +1654,125 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128627678</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grönskåra, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547162</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6323432</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>128582282</v>
       </c>
       <c r="B8" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>128582313</v>
       </c>
       <c r="B9" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128462844</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128462848</v>
       </c>
       <c r="B3" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128462835</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128462828</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128462822</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128462856</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>128582282</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>128582313</v>
       </c>
       <c r="B9" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128462844</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128462848</v>
       </c>
       <c r="B3" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128462835</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128462828</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128462822</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128462856</v>
       </c>
       <c r="B7" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>128582282</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>128582313</v>
       </c>
       <c r="B9" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128462844</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128462848</v>
       </c>
       <c r="B3" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128462835</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128462828</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128462822</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128462856</v>
       </c>
       <c r="B7" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128462844</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128462848</v>
       </c>
       <c r="B3" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128462835</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128462828</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128462822</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128462856</v>
       </c>
       <c r="B7" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>128582282</v>
       </c>
       <c r="B8" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>128582313</v>
       </c>
       <c r="B9" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40170-2025 artfynd.xlsx
+++ b/artfynd/A 40170-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>128627678</v>
       </c>
       <c r="B10" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
